--- a/tools/songlist.xlsx
+++ b/tools/songlist.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PersonalWeb\WebPage\tools\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7372F573-ABB7-49E5-BD1A-FF7D1C175C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="171">
   <si>
     <t>id</t>
   </si>
@@ -271,29 +277,6 @@
     <t>rosso(Live at Kyoto Concert Hall 2019.10.19)</t>
   </si>
   <si>
-    <r>
-      <t>ジズー（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16.5"/>
-        <color rgb="FF18191C"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>jizue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16.5"/>
-        <color rgb="FF18191C"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
     <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=114375448860074&amp;bvid=BV1sj5yznEeW&amp;cid=29535241464&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
   </si>
   <si>
@@ -553,19 +536,26 @@
   </si>
   <si>
     <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=322843549&amp;bvid=BV1ow411q79w&amp;cid=1316476199&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
+  </si>
+  <si>
+    <t>ジズー（jizue）</t>
+  </si>
+  <si>
+    <t>Journey (feat. 小鳥遊めぐみ)</t>
+  </si>
+  <si>
+    <t>Lafale &amp; Soleily</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=244458972&amp;bvid=BV1xv41117oV&amp;cid=231145397&amp;p=3" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -586,375 +576,50 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Noto Sans CJK SC Medium"/>
+      <name val="Noto Sans CJK JP Medium"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Noto Sans CJK SC"/>
+      <name val="Noto Sans CJK JP Medium"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="16.5"/>
       <color rgb="FF18191C"/>
-      <name val="MS Gothic"/>
+      <name val="Noto Sans CJK JP Medium"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="16.5"/>
-      <color rgb="FF18191C"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16.5"/>
-      <color rgb="FF18191C"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -962,274 +627,32 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
       <extLst>
         <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
@@ -1237,10 +660,10 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
       <extLst>
         <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
@@ -1248,62 +671,21 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1553,23 +935,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" outlineLevelCol="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D62"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.90909090909091" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.90625" style="2" customWidth="1"/>
     <col min="2" max="2" width="51" style="2" customWidth="1"/>
-    <col min="3" max="3" width="46.3636363636364" style="2" customWidth="1"/>
-    <col min="4" max="4" width="93.7272727272727" style="2" customWidth="1"/>
+    <col min="3" max="3" width="46.36328125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="93.7265625" style="2" customWidth="1"/>
     <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:4">
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1583,879 +965,891 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="29" ht="21.5" spans="1:4">
-      <c r="A29" s="2">
+    <row r="29" spans="1:4" ht="27" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="5" t="s">
         <v>79</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D29" s="2" t="s">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="C30" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D30" s="2" t="s">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="C31" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="2" t="s">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="C32" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D32" s="2" t="s">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="C33" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="D33" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D33" s="2" t="s">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="C34" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D34" s="2" t="s">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="C35" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D35" s="2" t="s">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="C36" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="D36" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="2" t="s">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" s="7" t="s">
+      <c r="C37" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D37" s="2" t="s">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="C38" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D38" s="2" t="s">
+    </row>
+    <row r="39" spans="1:4" ht="27" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="39" ht="20.5" spans="1:4">
-      <c r="A39" s="2">
-        <v>38</v>
-      </c>
-      <c r="B39" s="8" t="s">
+      <c r="C39" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D39" s="2" t="s">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="2">
+      <c r="C40" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="27" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <v>43</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <v>45</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>110</v>
-      </c>
-      <c r="C40" t="s">
-        <v>111</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="2">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>113</v>
-      </c>
-      <c r="C41" t="s">
-        <v>111</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="2">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="2">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="44" ht="20.5" spans="1:4">
-      <c r="A44" s="2">
-        <v>43</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="2">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>122</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="2">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>124</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="2">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>126</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="2">
-        <v>47</v>
-      </c>
-      <c r="B48" t="s">
+      <c r="D48" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C48" t="s">
-        <v>39</v>
-      </c>
-      <c r="D48" s="2" t="s">
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="2">
-        <v>48</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="C49" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="D49" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D49" s="2" t="s">
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
+        <v>49</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="2">
-        <v>49</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="C50" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D50" s="2" t="s">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="2">
-        <v>50</v>
-      </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D51" s="2" t="s">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
+        <v>51</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="2">
-        <v>51</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="C52" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="D52" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D52" s="2" t="s">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <v>52</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="2">
-        <v>52</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="C53" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D53" s="2" t="s">
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="4">
+        <v>53</v>
+      </c>
+      <c r="B54" s="5" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="2">
-        <v>53</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="C54" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D54" s="2" t="s">
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="4">
+        <v>54</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="2">
-        <v>54</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="C55" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D55" s="2" t="s">
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="4">
+        <v>55</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="2">
-        <v>55</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="C56" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D56" s="2" t="s">
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="4">
+        <v>56</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="2">
-        <v>56</v>
-      </c>
-      <c r="B57" t="s">
+      <c r="C57" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="D57" s="2" t="s">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="4">
+        <v>57</v>
+      </c>
+      <c r="B58" s="5" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="2">
-        <v>57</v>
-      </c>
-      <c r="B58" t="s">
+      <c r="C58" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C58" t="s">
-        <v>155</v>
-      </c>
-      <c r="D58" s="2" t="s">
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="4">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="2">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2" t="s">
+      <c r="C59" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D59" s="2" t="s">
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="4">
+        <v>59</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="2">
-        <v>59</v>
-      </c>
-      <c r="B60" t="s">
+      <c r="C60" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D60" s="2" t="s">
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="2">
-        <v>60</v>
-      </c>
-      <c r="B61" t="s">
+      <c r="C61" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>167</v>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C16" r:id="rId1" display="三月のパンタシア kemu（堀江晶太）" tooltip="三月のパンタシア"/>
-    <hyperlink ref="C31" r:id="rId2" display="ヨルシカ" tooltip="ヨルシカ"/>
-    <hyperlink ref="C36" r:id="rId3" display=" takehirotei" tooltip="takehirotei"/>
-    <hyperlink ref="C52" r:id="rId4" display="埼玉最終兵器" tooltip="埼玉最終兵器"/>
+    <hyperlink ref="C16" r:id="rId1" location="/m/artist/?id=12054234" tooltip="三月のパンタシア" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C31" r:id="rId2" location="/m/artist/?id=12390232" tooltip="ヨルシカ" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C36" r:id="rId3" location="/m/artist/?id=50267822" tooltip="takehirotei" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C52" r:id="rId4" location="/m/artist/?id=824039" tooltip="埼玉最終兵器" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/tools/songlist.xlsx
+++ b/tools/songlist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PersonalWeb\WebPage\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4FAC6F-19ED-496C-836B-E41A911BA9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B18B898-14A8-480F-9728-6A76D5380FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="18240" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="359">
   <si>
     <t>id</t>
   </si>
@@ -421,9 +421,6 @@
     <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=252837510&amp;bvid=BV1VY411a7Tt&amp;cid=474753029&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
   </si>
   <si>
-    <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=745502314&amp;bvid=BV1br4y197Z7&amp;cid=1254974916&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
-  </si>
-  <si>
     <t>かたぎり</t>
   </si>
   <si>
@@ -444,10 +441,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>时长</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>4:10</t>
   </si>
   <si>
@@ -585,18 +578,10 @@
     <t>3:01</t>
   </si>
   <si>
-    <t>来源</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>osu!mania 7k World Cup Semifinals Tiebreaker</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Lumbus Company</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>80</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -623,22 +608,6 @@
   </si>
   <si>
     <t>osu!mania 7K Chinese National Cup 2026</t>
-  </si>
-  <si>
-    <r>
-      <t>osu!mania 7K World Cup 2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Quaterfinals Tiebreaker</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1197,12 +1166,229 @@
   <si>
     <t>FRENZ2019</t>
   </si>
+  <si>
+    <t>Limbus Company</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>source</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>length</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>osu!ma+G4nia 7K World Cup 2026 Quaterfinals Tiebreaker</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=63789384&amp;bvid=BV1u4411U7We&amp;cid=110749900&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
+  </si>
+  <si>
+    <t>62</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>63</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>64</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>名の無い星が空に堕ちたら（倘若无名之星堕入天空）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>全てあなたの所為です。</t>
+  </si>
+  <si>
+    <t>100</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>アブジェ（Abject</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/凄惨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC Medium"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>~90</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>3:51</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>170-185（180）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=559980508&amp;bvid=BV12e4y1a7bJ&amp;cid=887515619&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
+  </si>
+  <si>
+    <t>K²（形而上）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>4:33</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>全て此の世の所為です。a.k.a 夏毛</t>
+  </si>
+  <si>
+    <t>65</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>150</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>5:28</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=840423192&amp;bvid=BV1u54y1R7PL&amp;cid=192006684&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
+  </si>
+  <si>
+    <t>猶狩</t>
+  </si>
+  <si>
+    <t>4:26</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=588877190&amp;bvid=BV1FB4y1T7LU&amp;cid=362146659&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
+  </si>
+  <si>
+    <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=619892510&amp;bvid=BV1y84y1d7RW&amp;cid=1307180388&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
+  </si>
+  <si>
+    <t>星間飛行</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>倘若塵世猶然絢麗</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>夢見</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t> ヒバナ（HIBANA）</t>
+  </si>
+  <si>
+    <t>167</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>3:08</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>週末キネマ</t>
+  </si>
+  <si>
+    <t>138</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>3:48</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>雨中曲</t>
+  </si>
+  <si>
+    <t>137</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>4:17</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Singin' In The Rain</t>
+  </si>
+  <si>
+    <t>Gene Kelly（吉恩·凯利）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=426248631&amp;bvid=BV1i3411P7qM&amp;cid=710379839&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>飛燕草-long mix-</t>
+  </si>
+  <si>
+    <t>2TORI</t>
+  </si>
+  <si>
+    <t>4:09</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=116391382359323&amp;bvid=BV14QDDB7E4G&amp;cid=37923064402&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
+  </si>
+  <si>
+    <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=425365125&amp;bvid=BV1e3411H7Gg&amp;cid=566064673&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
+  </si>
+  <si>
+    <t>BlackY（WAiKURO）/Risa Yuzuki（柚木梨莎）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=69198778&amp;bvid=BV1ZJ411T7aX&amp;cid=119929361&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=37111767&amp;bvid=BV1jt411X7rn&amp;cid=65252903&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1264,6 +1450,20 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1287,7 +1487,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1332,6 +1532,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1601,7 +1807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.90625" style="1" customWidth="1"/>
@@ -1624,13 +1830,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>135</v>
+        <v>307</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>176</v>
+        <v>306</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>3</v>
@@ -1641,19 +1847,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>5</v>
@@ -1670,13 +1876,13 @@
         <v>7</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>178</v>
+        <v>305</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>8</v>
@@ -1693,13 +1899,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>11</v>
@@ -1716,13 +1922,13 @@
         <v>13</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>187</v>
+        <v>308</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -1739,13 +1945,13 @@
         <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>17</v>
@@ -1762,13 +1968,13 @@
         <v>19</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>20</v>
@@ -1785,13 +1991,13 @@
         <v>22</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>23</v>
@@ -1808,10 +2014,10 @@
         <v>22</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>25</v>
@@ -1828,10 +2034,10 @@
         <v>27</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>28</v>
@@ -1842,16 +2048,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>29</v>
@@ -1862,16 +2068,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>31</v>
@@ -1888,13 +2094,13 @@
         <v>33</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>34</v>
@@ -1905,19 +2111,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>36</v>
@@ -1928,16 +2134,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>37</v>
@@ -1948,16 +2154,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>39</v>
@@ -1968,16 +2174,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>41</v>
@@ -1988,19 +2194,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>43</v>
@@ -2011,16 +2217,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>44</v>
@@ -2037,10 +2243,10 @@
         <v>40</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>46</v>
@@ -2051,16 +2257,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>47</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>48</v>
@@ -2074,13 +2280,13 @@
         <v>49</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>51</v>
@@ -2097,10 +2303,10 @@
         <v>50</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>53</v>
@@ -2111,19 +2317,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>54</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2131,19 +2337,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>55</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>56</v>
@@ -2160,10 +2366,10 @@
         <v>58</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="5" t="s">
@@ -2181,10 +2387,10 @@
         <v>61</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F27" s="11"/>
       <c r="G27" s="5" t="s">
@@ -2196,16 +2402,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>63</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="5" t="s">
@@ -2220,13 +2426,13 @@
         <v>65</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>66</v>
@@ -2237,16 +2443,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>67</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E30" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="5" t="s">
@@ -2258,16 +2464,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>69</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>70</v>
@@ -2278,16 +2484,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="5" t="s">
@@ -2299,16 +2505,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>73</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>74</v>
@@ -2319,16 +2525,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>75</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>76</v>
@@ -2339,16 +2545,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>75</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>77</v>
@@ -2365,10 +2571,10 @@
         <v>79</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>80</v>
@@ -2385,13 +2591,13 @@
         <v>82</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>83</v>
@@ -2408,13 +2614,13 @@
         <v>61</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>85</v>
@@ -2425,19 +2631,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>86</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>87</v>
@@ -2448,16 +2654,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>88</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>89</v>
@@ -2468,16 +2674,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>88</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>90</v>
@@ -2494,10 +2700,10 @@
         <v>92</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>93</v>
@@ -2514,10 +2720,10 @@
         <v>92</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>95</v>
@@ -2534,13 +2740,13 @@
         <v>92</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>97</v>
@@ -2557,13 +2763,13 @@
         <v>92</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>99</v>
@@ -2580,13 +2786,13 @@
         <v>92</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>101</v>
@@ -2603,13 +2809,13 @@
         <v>92</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>103</v>
@@ -2620,19 +2826,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>104</v>
@@ -2643,16 +2849,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>105</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>106</v>
@@ -2669,10 +2875,10 @@
         <v>108</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>109</v>
@@ -2689,13 +2895,13 @@
         <v>111</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>112</v>
@@ -2712,10 +2918,10 @@
         <v>114</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>115</v>
@@ -2726,16 +2932,16 @@
         <v>52</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>116</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>117</v>
@@ -2746,16 +2952,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>118</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>119</v>
@@ -2766,16 +2972,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>120</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>121</v>
@@ -2792,10 +2998,10 @@
         <v>123</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>124</v>
@@ -2806,19 +3012,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>125</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>126</v>
@@ -2829,16 +3035,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>125</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>127</v>
@@ -2849,19 +3055,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>128</v>
+        <v>309</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -2869,22 +3075,22 @@
         <v>59</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C60" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G60" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -2892,19 +3098,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -2912,19 +3118,202 @@
         <v>61</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>305</v>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="G70" s="11" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>

--- a/tools/songlist.xlsx
+++ b/tools/songlist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PersonalWeb\WebPage\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B18B898-14A8-480F-9728-6A76D5380FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEEFA0F4-C5B7-4FAE-B21E-12179566F648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3277,11 +3277,11 @@
       <c r="A70" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C70" s="11" t="s">
         <v>349</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>346</v>

--- a/tools/songlist.xlsx
+++ b/tools/songlist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PersonalWeb\WebPage\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27EAC66-D71A-4D52-9548-62563464183D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA53A22C-24C4-45B7-86C5-5E19487BA9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="523">
   <si>
     <t>id</t>
   </si>
@@ -1910,6 +1910,9 @@
   </si>
   <si>
     <t>160</t>
+  </si>
+  <si>
+    <t>&lt;iframe src="//player.bilibili.com/player.html?isOutside=true&amp;aid=5645721&amp;bvid=BV16s411C7Xr&amp;cid=9175868&amp;p=1" scrolling="no" border="0" frameborder="no" framespacing="0" allowfullscreen="true"&gt;&lt;/iframe&gt;</t>
   </si>
 </sst>
 </file>
@@ -4510,7 +4513,9 @@
         <v>520</v>
       </c>
       <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
+      <c r="G101" s="4" t="s">
+        <v>522</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
